--- a/output/differences_relative_regional.xlsx
+++ b/output/differences_relative_regional.xlsx
@@ -428,10 +428,10 @@
         <v>7.123738108385654</v>
       </c>
       <c r="G2">
-        <v>22.14352243759903</v>
+        <v>23.67410289139176</v>
       </c>
       <c r="H2">
-        <v>-2.314816478646988</v>
+        <v>-2.267037605644267</v>
       </c>
       <c r="I2" s="2">
         <v>41395</v>
@@ -457,10 +457,10 @@
         <v>-5.626246120072666</v>
       </c>
       <c r="G3">
-        <v>7.842776362136834</v>
+        <v>6.817096582105396</v>
       </c>
       <c r="H3">
-        <v>0.3609137299016283</v>
+        <v>1.772338011963755</v>
       </c>
       <c r="I3" s="2">
         <v>41426</v>
@@ -486,10 +486,10 @@
         <v>-7.017960535784301</v>
       </c>
       <c r="G4">
-        <v>13.31080108432491</v>
+        <v>16.85239817543223</v>
       </c>
       <c r="H4">
-        <v>14.24052521746305</v>
+        <v>14.55086415370442</v>
       </c>
       <c r="I4" s="2">
         <v>41456</v>
@@ -515,10 +515,10 @@
         <v>3.901343642395511</v>
       </c>
       <c r="G5">
-        <v>-1.2914815887232</v>
+        <v>-2.600990807939012</v>
       </c>
       <c r="H5">
-        <v>-1.741043987901065</v>
+        <v>-2.986620782692119</v>
       </c>
       <c r="I5" s="2">
         <v>41487</v>
@@ -544,10 +544,10 @@
         <v>6.622149199299004</v>
       </c>
       <c r="G6">
-        <v>19.37607699753414</v>
+        <v>19.95567453078842</v>
       </c>
       <c r="H6">
-        <v>12.76233041266255</v>
+        <v>15.08619008365472</v>
       </c>
       <c r="I6" s="2">
         <v>41518</v>
@@ -573,10 +573,10 @@
         <v>9.254173819038428</v>
       </c>
       <c r="G7">
-        <v>-17.51643748692711</v>
+        <v>-16.48283598254772</v>
       </c>
       <c r="H7">
-        <v>-2.310324131809042</v>
+        <v>-2.262543061551208</v>
       </c>
       <c r="I7" s="2">
         <v>41760</v>
@@ -602,10 +602,10 @@
         <v>6.462919037138502</v>
       </c>
       <c r="G8">
-        <v>16.17214653226588</v>
+        <v>15.06724710626381</v>
       </c>
       <c r="H8">
-        <v>-11.63105573338177</v>
+        <v>-10.38828034321572</v>
       </c>
       <c r="I8" s="2">
         <v>41791</v>
@@ -631,10 +631,10 @@
         <v>9.663023011711132</v>
       </c>
       <c r="G9">
-        <v>-12.35638695731089</v>
+        <v>-9.617033232548788</v>
       </c>
       <c r="H9">
-        <v>13.68734960828658</v>
+        <v>13.99618582095608</v>
       </c>
       <c r="I9" s="2">
         <v>41821</v>
@@ -660,10 +660,10 @@
         <v>14.40116328376719</v>
       </c>
       <c r="G10">
-        <v>6.847933086010276</v>
+        <v>5.430442927285537</v>
       </c>
       <c r="H10">
-        <v>8.65694014656331</v>
+        <v>7.279553608659377</v>
       </c>
       <c r="I10" s="2">
         <v>41852</v>
@@ -689,10 +689,10 @@
         <v>5.366158676381872</v>
       </c>
       <c r="G11">
-        <v>10.76025239586326</v>
+        <v>11.29801817512061</v>
       </c>
       <c r="H11">
-        <v>3.594014980214824</v>
+        <v>5.728929651521105</v>
       </c>
       <c r="I11" s="2">
         <v>41883</v>
@@ -718,10 +718,10 @@
         <v>12.19097339245348</v>
       </c>
       <c r="G12">
-        <v>-26.22332434954664</v>
+        <v>-25.29882884259842</v>
       </c>
       <c r="H12">
-        <v>-6.943730660446866</v>
+        <v>-6.898215839113601</v>
       </c>
       <c r="I12" s="2">
         <v>42125</v>
@@ -747,10 +747,10 @@
         <v>4.554000873688556</v>
       </c>
       <c r="G13">
-        <v>13.13849033053012</v>
+        <v>12.06244364673898</v>
       </c>
       <c r="H13">
-        <v>0.2919319533377569</v>
+        <v>1.702386111166818</v>
       </c>
       <c r="I13" s="2">
         <v>42156</v>
@@ -776,10 +776,10 @@
         <v>2.64466266039827</v>
       </c>
       <c r="G14">
-        <v>-10.39089331367629</v>
+        <v>-7.590106905495901</v>
       </c>
       <c r="H14">
-        <v>-0.4611904078791899</v>
+        <v>-0.1907892676117711</v>
       </c>
       <c r="I14" s="2">
         <v>42186</v>
@@ -805,10 +805,10 @@
         <v>6.469988993663149</v>
       </c>
       <c r="G15">
-        <v>28.11609770855801</v>
+        <v>26.41645502543834</v>
       </c>
       <c r="H15">
-        <v>14.85777475340103</v>
+        <v>13.40178351615892</v>
       </c>
       <c r="I15" s="2">
         <v>42217</v>
@@ -834,10 +834,10 @@
         <v>6.11920237148078</v>
       </c>
       <c r="G16">
-        <v>3.731538935941092</v>
+        <v>4.235178740499113</v>
       </c>
       <c r="H16">
-        <v>11.4150430790823</v>
+        <v>13.71113721269786</v>
       </c>
       <c r="I16" s="2">
         <v>42248</v>
@@ -863,10 +863,10 @@
         <v>7.513654603755808</v>
       </c>
       <c r="G17">
-        <v>2.295492412953193</v>
+        <v>3.577357206711354</v>
       </c>
       <c r="H17">
-        <v>10.77513864621611</v>
+        <v>10.8293199569374</v>
       </c>
       <c r="I17" s="2">
         <v>42491</v>
@@ -892,10 +892,10 @@
         <v>10.37379982279087</v>
       </c>
       <c r="G18">
-        <v>18.62042160128026</v>
+        <v>17.49223692318295</v>
       </c>
       <c r="H18">
-        <v>-1.006103183712543</v>
+        <v>0.3860960754382012</v>
       </c>
       <c r="I18" s="2">
         <v>42522</v>
@@ -921,10 +921,10 @@
         <v>4.000964853418719</v>
       </c>
       <c r="G19">
-        <v>-3.440075490134509</v>
+        <v>-0.4220370993619811</v>
       </c>
       <c r="H19">
-        <v>-5.758400041353378</v>
+        <v>-5.502388982010138</v>
       </c>
       <c r="I19" s="2">
         <v>42552</v>
@@ -950,10 +950,10 @@
         <v>-1.731452824732618</v>
       </c>
       <c r="G20">
-        <v>19.87827001034466</v>
+        <v>18.2879138557916</v>
       </c>
       <c r="H20">
-        <v>0.6627331797605833</v>
+        <v>-0.6133150263033442</v>
       </c>
       <c r="I20" s="2">
         <v>42583</v>
@@ -979,10 +979,10 @@
         <v>-6.228096709753796</v>
       </c>
       <c r="G21">
-        <v>20.26420136701001</v>
+        <v>20.84811094256554</v>
       </c>
       <c r="H21">
-        <v>8.562394007914081</v>
+        <v>10.79969939436806</v>
       </c>
       <c r="I21" s="2">
         <v>42614</v>
@@ -1008,10 +1008,10 @@
         <v>2.089642981010925</v>
       </c>
       <c r="G22">
-        <v>16.9431688500841</v>
+        <v>18.40858367417323</v>
       </c>
       <c r="H22">
-        <v>7.275086163212363</v>
+        <v>7.327555560652025</v>
       </c>
       <c r="I22" s="2">
         <v>42856</v>
@@ -1037,10 +1037,10 @@
         <v>4.564881566347402</v>
       </c>
       <c r="G23">
-        <v>5.112093425418944</v>
+        <v>4.112384845020417</v>
       </c>
       <c r="H23">
-        <v>-6.679223375211578</v>
+        <v>-5.366807961143075</v>
       </c>
       <c r="I23" s="2">
         <v>42887</v>
@@ -1066,10 +1066,10 @@
         <v>8.132014236540765</v>
       </c>
       <c r="G24">
-        <v>-13.35367883546484</v>
+        <v>-10.64549606687686</v>
       </c>
       <c r="H24">
-        <v>-7.41437707887748</v>
+        <v>-7.162864547103919</v>
       </c>
       <c r="I24" s="2">
         <v>42917</v>
@@ -1095,10 +1095,10 @@
         <v>13.76356697573533</v>
       </c>
       <c r="G25">
-        <v>10.57187422335847</v>
+        <v>9.10498067645951</v>
       </c>
       <c r="H25">
-        <v>6.870244004501883</v>
+        <v>5.515506468217919</v>
       </c>
       <c r="I25" s="2">
         <v>42948</v>
@@ -1124,10 +1124,10 @@
         <v>8.554707327442333</v>
       </c>
       <c r="G26">
-        <v>-6.380103157895485</v>
+        <v>-5.925557635560013</v>
       </c>
       <c r="H26">
-        <v>-14.9943470887507</v>
+        <v>-13.24251021305034</v>
       </c>
       <c r="I26" s="2">
         <v>42979</v>
